--- a/output/graficos_dimensiones/comunal_i_ingr_median_a_2024_maule.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_median_a_2024_maule.xlsx
@@ -117,12 +117,12 @@
     <t xml:space="preserve">Río Claro</t>
   </si>
   <si>
+    <t xml:space="preserve">Rauco</t>
+  </si>
+  <si>
     <t xml:space="preserve">Empedrado</t>
   </si>
   <si>
-    <t xml:space="preserve">Rauco</t>
-  </si>
-  <si>
     <t xml:space="preserve">Campo</t>
   </si>
   <si>
@@ -132,7 +132,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 20:23</t>
+    <t xml:space="preserve">2026-09-09 23:20</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -1038,7 +1038,7 @@
         <v>33</v>
       </c>
       <c r="C30" s="2" t="n">
-        <v>7104</v>
+        <v>7305</v>
       </c>
       <c r="D30" s="2" t="n">
         <v>2024</v>
@@ -1055,7 +1055,7 @@
         <v>34</v>
       </c>
       <c r="C31" s="2" t="n">
-        <v>7305</v>
+        <v>7104</v>
       </c>
       <c r="D31" s="2" t="n">
         <v>2024</v>

--- a/output/graficos_dimensiones/comunal_i_ingr_median_a_2024_maule.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_median_a_2024_maule.xlsx
@@ -132,7 +132,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 23:20</t>
+    <t xml:space="preserve">2026-09-17 14:15</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_median_a_2024_maule.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_median_a_2024_maule.xlsx
@@ -117,12 +117,12 @@
     <t xml:space="preserve">Río Claro</t>
   </si>
   <si>
+    <t xml:space="preserve">Empedrado</t>
+  </si>
+  <si>
     <t xml:space="preserve">Rauco</t>
   </si>
   <si>
-    <t xml:space="preserve">Empedrado</t>
-  </si>
-  <si>
     <t xml:space="preserve">Campo</t>
   </si>
   <si>
@@ -132,7 +132,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-17 14:15</t>
+    <t xml:space="preserve">2026-09-23 12:44</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -1038,7 +1038,7 @@
         <v>33</v>
       </c>
       <c r="C30" s="2" t="n">
-        <v>7305</v>
+        <v>7104</v>
       </c>
       <c r="D30" s="2" t="n">
         <v>2024</v>
@@ -1055,7 +1055,7 @@
         <v>34</v>
       </c>
       <c r="C31" s="2" t="n">
-        <v>7104</v>
+        <v>7305</v>
       </c>
       <c r="D31" s="2" t="n">
         <v>2024</v>

--- a/output/graficos_dimensiones/comunal_i_ingr_median_a_2024_maule.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_median_a_2024_maule.xlsx
@@ -132,7 +132,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 12:44</t>
+    <t xml:space="preserve">2026-10-02 14:53</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_median_a_2024_maule.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_median_a_2024_maule.xlsx
@@ -132,7 +132,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 14:53</t>
+    <t xml:space="preserve">2026-10-05 11:43</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
